--- a/hack2024/FileRecv/无名小妖版/恐龙快打主数据.xlsx
+++ b/hack2024/FileRecv/无名小妖版/恐龙快打主数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chern11\Documents\hack2024\FileRecv\无名小妖版\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chern11\Documents\GitHub\Cadillac-and-dinosaur\hack2024\FileRecv\无名小妖版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E75496B-0840-4F76-81E0-601DC1FB6777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43503A55-E44C-4053-8379-C951B16C55C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,6 +26,17 @@
     <sheet name="指令及地址" sheetId="1" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -3561,52 +3572,13 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="20" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="18" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
@@ -3621,10 +3593,49 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="21" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="20" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="18" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="18" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="12" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3640,6 +3651,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="3" borderId="0" xfId="10" applyNumberFormat="1" applyAlignment="1">
@@ -3671,9 +3685,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="26">
@@ -5577,16 +5588,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.5">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="70" t="s">
         <v>837</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="68" t="s">
         <v>838</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -5603,7 +5614,7 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="67"/>
+      <c r="A3" s="68"/>
       <c r="B3" s="5" t="s">
         <v>843</v>
       </c>
@@ -5621,12 +5632,12 @@
       <c r="A4" s="6" t="s">
         <v>847</v>
       </c>
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="71" t="s">
         <v>848</v>
       </c>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
     </row>
     <row r="5" spans="1:5" ht="49.5">
       <c r="A5" s="7" t="s">
@@ -5697,7 +5708,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="99">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="69" t="s">
         <v>867</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -5714,24 +5725,24 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="68"/>
-      <c r="B10" s="66" t="s">
+      <c r="A10" s="69"/>
+      <c r="B10" s="67" t="s">
         <v>872</v>
       </c>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="11" t="s">
         <v>873</v>
       </c>
-      <c r="B11" s="66" t="s">
+      <c r="B11" s="67" t="s">
         <v>874</v>
       </c>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="12" t="s">
@@ -5754,23 +5765,23 @@
       <c r="A13" s="13" t="s">
         <v>878</v>
       </c>
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="67" t="s">
         <v>879</v>
       </c>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="7" t="s">
         <v>880</v>
       </c>
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="67" t="s">
         <v>881</v>
       </c>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5871,7 +5882,7 @@
       <c r="A12" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="72" t="s">
         <v>899</v>
       </c>
     </row>
@@ -5879,13 +5890,13 @@
       <c r="A13" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="B13" s="71"/>
+      <c r="B13" s="72"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="B14" s="71"/>
+      <c r="B14" s="72"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
@@ -7368,45 +7379,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="26.5" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="E1" s="43" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="E1" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="I1" s="44" t="s">
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="I1" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="M1" s="40" t="s">
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="M1" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="Q1" s="43" t="s">
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="Q1" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="U1" s="40" t="s">
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="U1" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="V1" s="40"/>
-      <c r="W1" s="40"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
       <c r="X1" s="28"/>
-      <c r="Y1" s="44" t="s">
+      <c r="Y1" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="Z1" s="44"/>
-      <c r="AA1" s="44"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="38" t="s">
         <v>133</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -7415,7 +7426,7 @@
       <c r="C2" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="38" t="s">
         <v>136</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -7424,7 +7435,7 @@
       <c r="G2" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="53" t="s">
+      <c r="I2" s="40" t="s">
         <v>139</v>
       </c>
       <c r="J2" s="1" t="s">
@@ -7433,7 +7444,7 @@
       <c r="K2" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="M2" s="48" t="s">
+      <c r="M2" s="47" t="s">
         <v>139</v>
       </c>
       <c r="N2" s="1" t="s">
@@ -7442,7 +7453,7 @@
       <c r="O2" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="Q2" s="44" t="s">
+      <c r="Q2" s="37" t="s">
         <v>139</v>
       </c>
       <c r="R2" s="1" t="s">
@@ -7451,7 +7462,7 @@
       <c r="S2" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="U2" s="47" t="s">
+      <c r="U2" s="42" t="s">
         <v>146</v>
       </c>
       <c r="V2" s="1" t="s">
@@ -7460,7 +7471,7 @@
       <c r="W2" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="Y2" s="56" t="s">
+      <c r="Y2" s="44" t="s">
         <v>139</v>
       </c>
       <c r="Z2" s="1" t="s">
@@ -7471,49 +7482,49 @@
       </c>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="51"/>
+      <c r="A3" s="38"/>
       <c r="B3" s="1" t="s">
         <v>151</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E3" s="51"/>
+      <c r="E3" s="38"/>
       <c r="F3" s="1" t="s">
         <v>153</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="I3" s="53"/>
+      <c r="I3" s="40"/>
       <c r="J3" s="1" t="s">
         <v>155</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="M3" s="48"/>
+      <c r="M3" s="47"/>
       <c r="N3" s="1" t="s">
         <v>157</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="Q3" s="44"/>
+      <c r="Q3" s="37"/>
       <c r="R3" s="1" t="s">
         <v>159</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="U3" s="47"/>
+      <c r="U3" s="42"/>
       <c r="V3" s="1" t="s">
         <v>161</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="Y3" s="56"/>
+      <c r="Y3" s="44"/>
       <c r="Z3" s="1" t="s">
         <v>163</v>
       </c>
@@ -7522,7 +7533,7 @@
       </c>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="39" t="s">
         <v>165</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -7531,14 +7542,14 @@
       <c r="C4" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E4" s="51"/>
+      <c r="E4" s="38"/>
       <c r="F4" s="1" t="s">
         <v>168</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="I4" s="53"/>
+      <c r="I4" s="40"/>
       <c r="J4" s="1" t="s">
         <v>170</v>
       </c>
@@ -7554,21 +7565,21 @@
       <c r="O4" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="Q4" s="44"/>
+      <c r="Q4" s="37"/>
       <c r="R4" s="1" t="s">
         <v>175</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="U4" s="47"/>
+      <c r="U4" s="42"/>
       <c r="V4" s="1" t="s">
         <v>177</v>
       </c>
       <c r="W4" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="Y4" s="56"/>
+      <c r="Y4" s="44"/>
       <c r="Z4" s="1" t="s">
         <v>179</v>
       </c>
@@ -7577,14 +7588,14 @@
       </c>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="52"/>
+      <c r="A5" s="39"/>
       <c r="B5" s="1" t="s">
         <v>181</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E5" s="51"/>
+      <c r="E5" s="38"/>
       <c r="F5" s="1" t="s">
         <v>183</v>
       </c>
@@ -7598,21 +7609,21 @@
       <c r="O5" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="Q5" s="44"/>
+      <c r="Q5" s="37"/>
       <c r="R5" s="1" t="s">
         <v>187</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="U5" s="47"/>
+      <c r="U5" s="42"/>
       <c r="V5" s="1" t="s">
         <v>189</v>
       </c>
       <c r="W5" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="Y5" s="56"/>
+      <c r="Y5" s="44"/>
       <c r="Z5" s="1" t="s">
         <v>191</v>
       </c>
@@ -7621,21 +7632,21 @@
       </c>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="52"/>
+      <c r="A6" s="39"/>
       <c r="B6" s="1" t="s">
         <v>193</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E6" s="51"/>
+      <c r="E6" s="38"/>
       <c r="F6" s="1" t="s">
         <v>195</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="I6" s="54" t="s">
+      <c r="I6" s="41" t="s">
         <v>197</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -7651,7 +7662,7 @@
       <c r="O6" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="U6" s="47"/>
+      <c r="U6" s="42"/>
       <c r="V6" s="1" t="s">
         <v>202</v>
       </c>
@@ -7660,28 +7671,28 @@
       </c>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7" s="52"/>
+      <c r="A7" s="39"/>
       <c r="B7" s="1" t="s">
         <v>204</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E7" s="51"/>
+      <c r="E7" s="38"/>
       <c r="F7" s="1" t="s">
         <v>206</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="I7" s="54"/>
+      <c r="I7" s="41"/>
       <c r="J7" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="Q7" s="40" t="s">
+      <c r="Q7" s="35" t="s">
         <v>209</v>
       </c>
       <c r="R7" s="1" t="s">
@@ -7690,14 +7701,14 @@
       <c r="S7" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="U7" s="47"/>
+      <c r="U7" s="42"/>
       <c r="V7" s="1" t="s">
         <v>212</v>
       </c>
       <c r="W7" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="Y7" s="36" t="s">
+      <c r="Y7" s="45" t="s">
         <v>214</v>
       </c>
       <c r="Z7" s="1" t="s">
@@ -7708,7 +7719,7 @@
       </c>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="37" t="s">
         <v>217</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -7717,14 +7728,14 @@
       <c r="C8" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="I8" s="54"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="1" t="s">
         <v>220</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="M8" s="44" t="s">
+      <c r="M8" s="37" t="s">
         <v>222</v>
       </c>
       <c r="N8" s="1" t="s">
@@ -7733,21 +7744,21 @@
       <c r="O8" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="Q8" s="40"/>
+      <c r="Q8" s="35"/>
       <c r="R8" s="1" t="s">
         <v>225</v>
       </c>
       <c r="S8" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="U8" s="47"/>
+      <c r="U8" s="42"/>
       <c r="V8" s="1" t="s">
         <v>226</v>
       </c>
       <c r="W8" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="Y8" s="36"/>
+      <c r="Y8" s="45"/>
       <c r="Z8" s="1" t="s">
         <v>228</v>
       </c>
@@ -7756,14 +7767,14 @@
       </c>
     </row>
     <row r="9" spans="1:27">
-      <c r="A9" s="44"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="1" t="s">
         <v>230</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="48" t="s">
         <v>232</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -7772,26 +7783,26 @@
       <c r="G9" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="I9" s="54"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="1" t="s">
         <v>235</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="M9" s="44"/>
+      <c r="M9" s="37"/>
       <c r="N9" s="1" t="s">
         <v>237</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="Q9" s="40"/>
+      <c r="Q9" s="35"/>
       <c r="R9" s="1" t="s">
         <v>238</v>
       </c>
       <c r="S9" s="33"/>
-      <c r="Y9" s="36"/>
+      <c r="Y9" s="45"/>
       <c r="Z9" s="1" t="s">
         <v>239</v>
       </c>
@@ -7800,33 +7811,33 @@
       </c>
     </row>
     <row r="10" spans="1:27">
-      <c r="A10" s="44"/>
+      <c r="A10" s="37"/>
       <c r="B10" s="1" t="s">
         <v>241</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E10" s="41"/>
+      <c r="E10" s="48"/>
       <c r="F10" s="1" t="s">
         <v>243</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="I10" s="54"/>
+      <c r="I10" s="41"/>
       <c r="J10" s="1" t="s">
         <v>245</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="Q10" s="40"/>
+      <c r="Q10" s="35"/>
       <c r="R10" s="1" t="s">
         <v>247</v>
       </c>
       <c r="S10" s="33"/>
-      <c r="U10" s="55" t="s">
+      <c r="U10" s="43" t="s">
         <v>248</v>
       </c>
       <c r="V10" s="1" t="s">
@@ -7837,7 +7848,7 @@
       </c>
     </row>
     <row r="11" spans="1:27">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="35" t="s">
         <v>251</v>
       </c>
       <c r="B11" s="27" t="s">
@@ -7846,14 +7857,14 @@
       <c r="C11" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="E11" s="41"/>
+      <c r="E11" s="48"/>
       <c r="F11" s="1" t="s">
         <v>254</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="M11" s="46" t="s">
+      <c r="M11" s="50" t="s">
         <v>256</v>
       </c>
       <c r="N11" s="1" t="s">
@@ -7862,21 +7873,21 @@
       <c r="O11" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="Q11" s="40"/>
+      <c r="Q11" s="35"/>
       <c r="R11" s="1" t="s">
         <v>259</v>
       </c>
       <c r="S11" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="U11" s="55"/>
+      <c r="U11" s="43"/>
       <c r="V11" s="1" t="s">
         <v>260</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="Y11" s="38" t="s">
+      <c r="Y11" s="46" t="s">
         <v>262</v>
       </c>
       <c r="Z11" s="1" t="s">
@@ -7887,7 +7898,7 @@
       </c>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="40"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="1" t="s">
         <v>265</v>
       </c>
@@ -7900,28 +7911,28 @@
       <c r="K12" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="M12" s="46"/>
+      <c r="M12" s="50"/>
       <c r="N12" s="1" t="s">
         <v>269</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="Q12" s="40"/>
+      <c r="Q12" s="35"/>
       <c r="R12" s="1" t="s">
         <v>271</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="U12" s="55"/>
+      <c r="U12" s="43"/>
       <c r="V12" s="1" t="s">
         <v>273</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="Y12" s="38"/>
+      <c r="Y12" s="46"/>
       <c r="Z12" s="1" t="s">
         <v>275</v>
       </c>
@@ -7930,11 +7941,11 @@
       </c>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13" s="40"/>
+      <c r="A13" s="35"/>
       <c r="B13" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="E13" s="52" t="s">
+      <c r="E13" s="39" t="s">
         <v>277</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -7943,21 +7954,21 @@
       <c r="G13" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="Q13" s="40"/>
+      <c r="Q13" s="35"/>
       <c r="R13" s="1" t="s">
         <v>280</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="U13" s="55"/>
+      <c r="U13" s="43"/>
       <c r="V13" s="1" t="s">
         <v>282</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="Y13" s="38"/>
+      <c r="Y13" s="46"/>
       <c r="Z13" s="1" t="s">
         <v>284</v>
       </c>
@@ -7966,18 +7977,18 @@
       </c>
     </row>
     <row r="14" spans="1:27">
-      <c r="A14" s="40"/>
+      <c r="A14" s="35"/>
       <c r="B14" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E14" s="52"/>
+      <c r="E14" s="39"/>
       <c r="F14" s="1" t="s">
         <v>286</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I14" s="44" t="s">
+      <c r="I14" s="37" t="s">
         <v>288</v>
       </c>
       <c r="J14" s="1" t="s">
@@ -7986,7 +7997,7 @@
       <c r="K14" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="M14" s="50" t="s">
+      <c r="M14" s="51" t="s">
         <v>291</v>
       </c>
       <c r="N14" s="1" t="s">
@@ -7995,14 +8006,14 @@
       <c r="O14" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="U14" s="55"/>
+      <c r="U14" s="43"/>
       <c r="V14" s="1" t="s">
         <v>294</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="Y14" s="38"/>
+      <c r="Y14" s="46"/>
       <c r="Z14" s="1" t="s">
         <v>296</v>
       </c>
@@ -8011,35 +8022,35 @@
       </c>
     </row>
     <row r="15" spans="1:27">
-      <c r="A15" s="40"/>
+      <c r="A15" s="35"/>
       <c r="B15" s="1" t="s">
         <v>297</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="E15" s="52"/>
+      <c r="E15" s="39"/>
       <c r="F15" s="1" t="s">
         <v>299</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="I15" s="44"/>
+      <c r="I15" s="37"/>
       <c r="J15" s="1" t="s">
         <v>301</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="M15" s="50"/>
+      <c r="M15" s="51"/>
       <c r="N15" s="1" t="s">
         <v>303</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="Q15" s="45" t="s">
+      <c r="Q15" s="52" t="s">
         <v>304</v>
       </c>
       <c r="R15" s="1" t="s">
@@ -8048,14 +8059,14 @@
       <c r="S15" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="U15" s="55"/>
+      <c r="U15" s="43"/>
       <c r="V15" s="1" t="s">
         <v>307</v>
       </c>
       <c r="W15" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="Y15" s="38"/>
+      <c r="Y15" s="46"/>
       <c r="Z15" s="1" t="s">
         <v>308</v>
       </c>
@@ -8064,42 +8075,42 @@
       </c>
     </row>
     <row r="16" spans="1:27">
-      <c r="A16" s="40"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="1" t="s">
         <v>309</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="E16" s="52"/>
+      <c r="E16" s="39"/>
       <c r="F16" s="1" t="s">
         <v>311</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="I16" s="44"/>
+      <c r="I16" s="37"/>
       <c r="J16" s="1" t="s">
         <v>313</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="M16" s="50"/>
+      <c r="M16" s="51"/>
       <c r="N16" s="1" t="s">
         <v>315</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="Q16" s="45"/>
+      <c r="Q16" s="52"/>
       <c r="R16" s="1" t="s">
         <v>316</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="Y16" s="38"/>
+      <c r="Y16" s="46"/>
       <c r="Z16" s="1" t="s">
         <v>318</v>
       </c>
@@ -8108,28 +8119,28 @@
       </c>
     </row>
     <row r="17" spans="1:27">
-      <c r="A17" s="40"/>
+      <c r="A17" s="35"/>
       <c r="B17" s="1" t="s">
         <v>319</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="M17" s="50"/>
+      <c r="M17" s="51"/>
       <c r="N17" s="1" t="s">
         <v>321</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="Q17" s="45"/>
+      <c r="Q17" s="52"/>
       <c r="R17" s="1" t="s">
         <v>322</v>
       </c>
       <c r="S17" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="U17" s="40" t="s">
+      <c r="U17" s="35" t="s">
         <v>324</v>
       </c>
       <c r="V17" s="1" t="s">
@@ -8140,14 +8151,14 @@
       </c>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="40"/>
+      <c r="A18" s="35"/>
       <c r="B18" s="1" t="s">
         <v>327</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="E18" s="47" t="s">
+      <c r="E18" s="42" t="s">
         <v>329</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -8156,7 +8167,7 @@
       <c r="G18" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="I18" s="47" t="s">
+      <c r="I18" s="42" t="s">
         <v>329</v>
       </c>
       <c r="J18" s="1" t="s">
@@ -8165,21 +8176,21 @@
       <c r="K18" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="Q18" s="45"/>
+      <c r="Q18" s="52"/>
       <c r="R18" s="1" t="s">
         <v>334</v>
       </c>
       <c r="S18" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="U18" s="40"/>
+      <c r="U18" s="35"/>
       <c r="V18" s="1" t="s">
         <v>335</v>
       </c>
       <c r="W18" s="33" t="s">
         <v>336</v>
       </c>
-      <c r="Y18" s="39" t="s">
+      <c r="Y18" s="54" t="s">
         <v>337</v>
       </c>
       <c r="Z18" s="1" t="s">
@@ -8190,28 +8201,28 @@
       </c>
     </row>
     <row r="19" spans="1:27">
-      <c r="A19" s="40"/>
+      <c r="A19" s="35"/>
       <c r="B19" s="1" t="s">
         <v>339</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E19" s="47"/>
+      <c r="E19" s="42"/>
       <c r="F19" s="1" t="s">
         <v>341</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="I19" s="47"/>
+      <c r="I19" s="42"/>
       <c r="J19" s="1" t="s">
         <v>343</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="M19" s="45" t="s">
+      <c r="M19" s="52" t="s">
         <v>345</v>
       </c>
       <c r="N19" s="1" t="s">
@@ -8220,12 +8231,12 @@
       <c r="O19" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="U19" s="40"/>
+      <c r="U19" s="35"/>
       <c r="V19" s="1" t="s">
         <v>348</v>
       </c>
       <c r="W19" s="33"/>
-      <c r="Y19" s="39"/>
+      <c r="Y19" s="54"/>
       <c r="Z19" s="1" t="s">
         <v>349</v>
       </c>
@@ -8234,28 +8245,28 @@
       </c>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="40"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="1" t="s">
         <v>351</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="I20" s="47"/>
+      <c r="I20" s="42"/>
       <c r="J20" s="1" t="s">
         <v>352</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="M20" s="45"/>
+      <c r="M20" s="52"/>
       <c r="N20" s="1" t="s">
         <v>354</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="Q20" s="46" t="s">
+      <c r="Q20" s="50" t="s">
         <v>232</v>
       </c>
       <c r="R20" s="1" t="s">
@@ -8264,14 +8275,14 @@
       <c r="S20" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="U20" s="40"/>
+      <c r="U20" s="35"/>
       <c r="V20" s="1" t="s">
         <v>357</v>
       </c>
       <c r="W20" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="Y20" s="39"/>
+      <c r="Y20" s="54"/>
       <c r="Z20" s="1" t="s">
         <v>358</v>
       </c>
@@ -8280,14 +8291,14 @@
       </c>
     </row>
     <row r="21" spans="1:27">
-      <c r="A21" s="40"/>
+      <c r="A21" s="35"/>
       <c r="B21" s="1" t="s">
         <v>360</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="E21" s="40" t="s">
+      <c r="E21" s="35" t="s">
         <v>362</v>
       </c>
       <c r="F21" s="27" t="s">
@@ -8296,28 +8307,28 @@
       <c r="G21" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="I21" s="47"/>
+      <c r="I21" s="42"/>
       <c r="J21" s="1" t="s">
         <v>365</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="M21" s="45"/>
+      <c r="M21" s="52"/>
       <c r="N21" s="1" t="s">
         <v>367</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="Q21" s="46"/>
+      <c r="Q21" s="50"/>
       <c r="R21" s="1" t="s">
         <v>369</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="U21" s="40"/>
+      <c r="U21" s="35"/>
       <c r="V21" s="1" t="s">
         <v>371</v>
       </c>
@@ -8326,42 +8337,42 @@
       </c>
     </row>
     <row r="22" spans="1:27">
-      <c r="A22" s="40"/>
+      <c r="A22" s="35"/>
       <c r="B22" s="1" t="s">
         <v>373</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E22" s="40"/>
+      <c r="E22" s="35"/>
       <c r="F22" s="1" t="s">
         <v>374</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="I22" s="47"/>
+      <c r="I22" s="42"/>
       <c r="J22" s="1" t="s">
         <v>375</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="Q22" s="46"/>
+      <c r="Q22" s="50"/>
       <c r="R22" s="1" t="s">
         <v>376</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="U22" s="40"/>
+      <c r="U22" s="35"/>
       <c r="V22" s="1" t="s">
         <v>377</v>
       </c>
       <c r="W22" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="Y22" s="37" t="s">
+      <c r="Y22" s="55" t="s">
         <v>378</v>
       </c>
       <c r="Z22" s="1" t="s">
@@ -8372,11 +8383,11 @@
       </c>
     </row>
     <row r="23" spans="1:27">
-      <c r="E23" s="40"/>
+      <c r="E23" s="35"/>
       <c r="F23" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="M23" s="43" t="s">
+      <c r="M23" s="36" t="s">
         <v>381</v>
       </c>
       <c r="N23" s="1" t="s">
@@ -8385,14 +8396,14 @@
       <c r="O23" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="U23" s="40"/>
+      <c r="U23" s="35"/>
       <c r="V23" s="1" t="s">
         <v>384</v>
       </c>
       <c r="W23" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="Y23" s="37"/>
+      <c r="Y23" s="55"/>
       <c r="Z23" s="1" t="s">
         <v>386</v>
       </c>
@@ -8401,12 +8412,12 @@
       </c>
     </row>
     <row r="24" spans="1:27">
-      <c r="A24" s="43" t="s">
+      <c r="A24" s="36" t="s">
         <v>387</v>
       </c>
-      <c r="B24" s="43"/>
-      <c r="C24" s="43"/>
-      <c r="E24" s="40"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="E24" s="35"/>
       <c r="F24" s="1" t="s">
         <v>388</v>
       </c>
@@ -8417,14 +8428,14 @@
       <c r="K24" s="27" t="s">
         <v>390</v>
       </c>
-      <c r="M24" s="43"/>
+      <c r="M24" s="36"/>
       <c r="N24" s="1" t="s">
         <v>391</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="Q24" s="43" t="s">
+      <c r="Q24" s="36" t="s">
         <v>393</v>
       </c>
       <c r="R24" s="1" t="s">
@@ -8433,7 +8444,7 @@
       <c r="S24" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="U24" s="40"/>
+      <c r="U24" s="35"/>
       <c r="V24" s="1" t="s">
         <v>396</v>
       </c>
@@ -8442,38 +8453,38 @@
       </c>
     </row>
     <row r="25" spans="1:27">
-      <c r="A25" s="43"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="43"/>
-      <c r="E25" s="40"/>
+      <c r="A25" s="36"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="E25" s="35"/>
       <c r="F25" s="1" t="s">
         <v>398</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="M25" s="43"/>
+      <c r="M25" s="36"/>
       <c r="N25" s="1" t="s">
         <v>400</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="Q25" s="43"/>
+      <c r="Q25" s="36"/>
       <c r="R25" s="1" t="s">
         <v>402</v>
       </c>
       <c r="S25" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="U25" s="40"/>
+      <c r="U25" s="35"/>
       <c r="V25" s="1" t="s">
         <v>404</v>
       </c>
       <c r="W25" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="Y25" s="38" t="s">
+      <c r="Y25" s="46" t="s">
         <v>405</v>
       </c>
       <c r="Z25" s="1" t="s">
@@ -8491,18 +8502,18 @@
       <c r="C26" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="E26" s="40"/>
+      <c r="E26" s="35"/>
       <c r="F26" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="M26" s="43"/>
+      <c r="M26" s="36"/>
       <c r="N26" s="1" t="s">
         <v>411</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="Y26" s="38"/>
+      <c r="Y26" s="46"/>
       <c r="Z26" s="1" t="s">
         <v>413</v>
       </c>
@@ -8518,7 +8529,7 @@
       <c r="C27" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="E27" s="40"/>
+      <c r="E27" s="35"/>
       <c r="F27" s="1" t="s">
         <v>416</v>
       </c>
@@ -8529,7 +8540,7 @@
       <c r="S27" s="27" t="s">
         <v>418</v>
       </c>
-      <c r="U27" s="41" t="s">
+      <c r="U27" s="48" t="s">
         <v>419</v>
       </c>
       <c r="V27" s="1" t="s">
@@ -8547,11 +8558,11 @@
       <c r="C28" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="E28" s="40"/>
+      <c r="E28" s="35"/>
       <c r="F28" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="M28" s="40" t="s">
+      <c r="M28" s="35" t="s">
         <v>425</v>
       </c>
       <c r="N28" s="27" t="s">
@@ -8560,14 +8571,14 @@
       <c r="O28" s="27" t="s">
         <v>427</v>
       </c>
-      <c r="U28" s="41"/>
+      <c r="U28" s="48"/>
       <c r="V28" s="1" t="s">
         <v>428</v>
       </c>
       <c r="W28" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="Y28" s="36" t="s">
+      <c r="Y28" s="45" t="s">
         <v>429</v>
       </c>
       <c r="Z28" s="1" t="s">
@@ -8585,15 +8596,15 @@
       <c r="C29" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="E29" s="40"/>
+      <c r="E29" s="35"/>
       <c r="F29" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="M29" s="40"/>
+      <c r="M29" s="35"/>
       <c r="N29" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="Y29" s="36"/>
+      <c r="Y29" s="45"/>
       <c r="Z29" s="1" t="s">
         <v>436</v>
       </c>
@@ -8609,15 +8620,15 @@
       <c r="C30" s="27" t="s">
         <v>438</v>
       </c>
-      <c r="E30" s="40"/>
+      <c r="E30" s="35"/>
       <c r="F30" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="M30" s="40"/>
+      <c r="M30" s="35"/>
       <c r="N30" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="U30" s="42" t="s">
+      <c r="U30" s="53" t="s">
         <v>441</v>
       </c>
       <c r="V30" s="1" t="s">
@@ -8626,7 +8637,7 @@
       <c r="W30" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="Y30" s="36"/>
+      <c r="Y30" s="45"/>
       <c r="Z30" s="1" t="s">
         <v>444</v>
       </c>
@@ -8635,15 +8646,15 @@
       </c>
     </row>
     <row r="31" spans="1:27">
-      <c r="E31" s="40"/>
+      <c r="E31" s="35"/>
       <c r="F31" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="M31" s="40"/>
+      <c r="M31" s="35"/>
       <c r="N31" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="U31" s="42"/>
+      <c r="U31" s="53"/>
       <c r="V31" s="1" t="s">
         <v>448</v>
       </c>
@@ -8652,22 +8663,22 @@
       </c>
     </row>
     <row r="32" spans="1:27">
-      <c r="E32" s="40"/>
+      <c r="E32" s="35"/>
       <c r="F32" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="M32" s="40"/>
+      <c r="M32" s="35"/>
       <c r="N32" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="U32" s="42"/>
+      <c r="U32" s="53"/>
       <c r="V32" s="1" t="s">
         <v>452</v>
       </c>
       <c r="W32" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="Y32" s="39" t="s">
+      <c r="Y32" s="54" t="s">
         <v>454</v>
       </c>
       <c r="Z32" s="1" t="s">
@@ -8678,22 +8689,22 @@
       </c>
     </row>
     <row r="33" spans="5:27">
-      <c r="E33" s="40"/>
+      <c r="E33" s="35"/>
       <c r="F33" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="M33" s="40"/>
+      <c r="M33" s="35"/>
       <c r="N33" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="U33" s="42"/>
+      <c r="U33" s="53"/>
       <c r="V33" s="1" t="s">
         <v>458</v>
       </c>
       <c r="W33" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="Y33" s="39"/>
+      <c r="Y33" s="54"/>
       <c r="Z33" s="1" t="s">
         <v>460</v>
       </c>
@@ -8702,15 +8713,15 @@
       </c>
     </row>
     <row r="34" spans="5:27">
-      <c r="E34" s="40"/>
+      <c r="E34" s="35"/>
       <c r="F34" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="M34" s="40"/>
+      <c r="M34" s="35"/>
       <c r="N34" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="U34" s="42"/>
+      <c r="U34" s="53"/>
       <c r="V34" s="1" t="s">
         <v>464</v>
       </c>
@@ -8719,22 +8730,22 @@
       </c>
     </row>
     <row r="35" spans="5:27">
-      <c r="E35" s="40"/>
+      <c r="E35" s="35"/>
       <c r="F35" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="M35" s="40"/>
+      <c r="M35" s="35"/>
       <c r="N35" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="U35" s="42"/>
+      <c r="U35" s="53"/>
       <c r="V35" s="1" t="s">
         <v>467</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="Y35" s="35" t="s">
+      <c r="Y35" s="56" t="s">
         <v>469</v>
       </c>
       <c r="Z35" s="1" t="s">
@@ -8745,22 +8756,22 @@
       </c>
     </row>
     <row r="36" spans="5:27">
-      <c r="E36" s="40"/>
+      <c r="E36" s="35"/>
       <c r="F36" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="M36" s="40"/>
+      <c r="M36" s="35"/>
       <c r="N36" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="U36" s="42"/>
+      <c r="U36" s="53"/>
       <c r="V36" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W36" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="Y36" s="35"/>
+      <c r="Y36" s="56"/>
       <c r="Z36" s="1" t="s">
         <v>476</v>
       </c>
@@ -8769,22 +8780,22 @@
       </c>
     </row>
     <row r="37" spans="5:27">
-      <c r="E37" s="40"/>
+      <c r="E37" s="35"/>
       <c r="F37" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="M37" s="40"/>
+      <c r="M37" s="35"/>
       <c r="N37" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="U37" s="42"/>
+      <c r="U37" s="53"/>
       <c r="V37" s="1" t="s">
         <v>479</v>
       </c>
       <c r="W37" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="Y37" s="35"/>
+      <c r="Y37" s="56"/>
       <c r="Z37" s="1" t="s">
         <v>481</v>
       </c>
@@ -8793,22 +8804,22 @@
       </c>
     </row>
     <row r="38" spans="5:27">
-      <c r="E38" s="40"/>
+      <c r="E38" s="35"/>
       <c r="F38" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="M38" s="40"/>
+      <c r="M38" s="35"/>
       <c r="N38" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="U38" s="42"/>
+      <c r="U38" s="53"/>
       <c r="V38" s="1" t="s">
         <v>485</v>
       </c>
       <c r="W38" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="Y38" s="35"/>
+      <c r="Y38" s="56"/>
       <c r="Z38" s="1" t="s">
         <v>487</v>
       </c>
@@ -8817,15 +8828,15 @@
       </c>
     </row>
     <row r="39" spans="5:27">
-      <c r="E39" s="40"/>
+      <c r="E39" s="35"/>
       <c r="F39" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="M39" s="40"/>
+      <c r="M39" s="35"/>
       <c r="N39" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="U39" s="42"/>
+      <c r="U39" s="53"/>
       <c r="V39" s="1" t="s">
         <v>491</v>
       </c>
@@ -8834,15 +8845,15 @@
       </c>
     </row>
     <row r="40" spans="5:27">
-      <c r="E40" s="40"/>
+      <c r="E40" s="35"/>
       <c r="F40" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="M40" s="40"/>
+      <c r="M40" s="35"/>
       <c r="N40" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="Y40" s="36" t="s">
+      <c r="Y40" s="45" t="s">
         <v>495</v>
       </c>
       <c r="Z40" s="1" t="s">
@@ -8853,15 +8864,15 @@
       </c>
     </row>
     <row r="41" spans="5:27">
-      <c r="E41" s="40"/>
+      <c r="E41" s="35"/>
       <c r="F41" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="M41" s="40"/>
+      <c r="M41" s="35"/>
       <c r="N41" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="U41" s="40" t="s">
+      <c r="U41" s="35" t="s">
         <v>500</v>
       </c>
       <c r="V41" s="27" t="s">
@@ -8871,7 +8882,7 @@
         <v>502</v>
       </c>
       <c r="X41"/>
-      <c r="Y41" s="36"/>
+      <c r="Y41" s="45"/>
       <c r="Z41" s="1" t="s">
         <v>503</v>
       </c>
@@ -8880,25 +8891,25 @@
       </c>
     </row>
     <row r="42" spans="5:27">
-      <c r="M42" s="40"/>
+      <c r="M42" s="35"/>
       <c r="N42" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="U42" s="40"/>
+      <c r="U42" s="35"/>
       <c r="V42" s="1" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="43" spans="5:27">
-      <c r="M43" s="40"/>
+      <c r="M43" s="35"/>
       <c r="N43" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="U43" s="40"/>
+      <c r="U43" s="35"/>
       <c r="V43" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="Y43" s="37" t="s">
+      <c r="Y43" s="55" t="s">
         <v>509</v>
       </c>
       <c r="Z43" s="1" t="s">
@@ -8909,12 +8920,12 @@
       </c>
     </row>
     <row r="44" spans="5:27">
-      <c r="M44" s="40"/>
+      <c r="M44" s="35"/>
       <c r="N44" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="U44" s="40"/>
-      <c r="Y44" s="37"/>
+      <c r="U44" s="35"/>
+      <c r="Y44" s="55"/>
       <c r="Z44" s="1" t="s">
         <v>512</v>
       </c>
@@ -8923,12 +8934,12 @@
       </c>
     </row>
     <row r="45" spans="5:27">
-      <c r="M45" s="40"/>
+      <c r="M45" s="35"/>
       <c r="N45" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="U45" s="40"/>
-      <c r="Y45" s="37"/>
+      <c r="U45" s="35"/>
+      <c r="Y45" s="55"/>
       <c r="Z45" s="1" t="s">
         <v>514</v>
       </c>
@@ -8937,19 +8948,19 @@
       </c>
     </row>
     <row r="46" spans="5:27">
-      <c r="M46" s="40"/>
+      <c r="M46" s="35"/>
       <c r="N46" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="U46" s="40"/>
+      <c r="U46" s="35"/>
     </row>
     <row r="47" spans="5:27">
-      <c r="M47" s="40"/>
+      <c r="M47" s="35"/>
       <c r="N47" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="U47" s="40"/>
-      <c r="Y47" s="38" t="s">
+      <c r="U47" s="35"/>
+      <c r="Y47" s="46" t="s">
         <v>517</v>
       </c>
       <c r="Z47" s="1" t="s">
@@ -8960,11 +8971,11 @@
       </c>
     </row>
     <row r="48" spans="5:27">
-      <c r="M48" s="40"/>
+      <c r="M48" s="35"/>
       <c r="N48" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="Y48" s="38"/>
+      <c r="Y48" s="46"/>
       <c r="Z48" s="1" t="s">
         <v>520</v>
       </c>
@@ -8973,11 +8984,11 @@
       </c>
     </row>
     <row r="49" spans="13:27">
-      <c r="M49" s="40"/>
+      <c r="M49" s="35"/>
       <c r="N49" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="Y49" s="38"/>
+      <c r="Y49" s="46"/>
       <c r="Z49" s="1" t="s">
         <v>523</v>
       </c>
@@ -8986,17 +8997,17 @@
       </c>
     </row>
     <row r="50" spans="13:27">
-      <c r="M50" s="40"/>
+      <c r="M50" s="35"/>
       <c r="N50" s="1" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="51" spans="13:27">
-      <c r="M51" s="40"/>
+      <c r="M51" s="35"/>
       <c r="N51" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="Y51" s="39" t="s">
+      <c r="Y51" s="54" t="s">
         <v>526</v>
       </c>
       <c r="Z51" s="29" t="s">
@@ -9007,64 +9018,82 @@
       </c>
     </row>
     <row r="52" spans="13:27">
-      <c r="M52" s="40"/>
+      <c r="M52" s="35"/>
       <c r="N52" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="Y52" s="39"/>
+      <c r="Y52" s="54"/>
       <c r="Z52" s="1" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="53" spans="13:27">
-      <c r="M53" s="40"/>
+      <c r="M53" s="35"/>
       <c r="N53" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="Y53" s="39"/>
+      <c r="Y53" s="54"/>
       <c r="Z53" s="1" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="54" spans="13:27">
-      <c r="M54" s="40"/>
-      <c r="Y54" s="39"/>
+      <c r="M54" s="35"/>
+      <c r="Y54" s="54"/>
     </row>
     <row r="55" spans="13:27">
-      <c r="M55" s="40"/>
-      <c r="Y55" s="39"/>
+      <c r="M55" s="35"/>
+      <c r="Y55" s="54"/>
       <c r="Z55" s="1" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="56" spans="13:27">
-      <c r="Y56" s="39"/>
+      <c r="Y56" s="54"/>
     </row>
     <row r="57" spans="13:27">
-      <c r="Y57" s="39"/>
+      <c r="Y57" s="54"/>
     </row>
     <row r="58" spans="13:27">
-      <c r="Y58" s="39"/>
+      <c r="Y58" s="54"/>
     </row>
     <row r="59" spans="13:27">
-      <c r="Y59" s="39"/>
+      <c r="Y59" s="54"/>
     </row>
     <row r="60" spans="13:27">
-      <c r="Y60" s="39"/>
+      <c r="Y60" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="U1:W1"/>
-    <mergeCell ref="Y1:AA1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="I6:I10"/>
-    <mergeCell ref="S8:S10"/>
-    <mergeCell ref="U2:U8"/>
+    <mergeCell ref="Y35:Y38"/>
+    <mergeCell ref="Y40:Y41"/>
+    <mergeCell ref="Y43:Y45"/>
+    <mergeCell ref="Y47:Y49"/>
+    <mergeCell ref="Y51:Y60"/>
+    <mergeCell ref="Y18:Y20"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="Y25:Y26"/>
+    <mergeCell ref="Y28:Y30"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="U17:U25"/>
+    <mergeCell ref="U27:U28"/>
+    <mergeCell ref="U30:U39"/>
+    <mergeCell ref="U41:U47"/>
+    <mergeCell ref="W18:W19"/>
+    <mergeCell ref="M23:M26"/>
+    <mergeCell ref="M28:M55"/>
+    <mergeCell ref="Q2:Q5"/>
+    <mergeCell ref="Q7:Q13"/>
+    <mergeCell ref="Q15:Q18"/>
+    <mergeCell ref="Q20:Q22"/>
+    <mergeCell ref="Q24:Q25"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="E13:E16"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="E21:E41"/>
+    <mergeCell ref="A24:C25"/>
     <mergeCell ref="U10:U15"/>
     <mergeCell ref="Y2:Y5"/>
     <mergeCell ref="Y7:Y9"/>
@@ -9073,13 +9102,6 @@
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A11:A22"/>
-    <mergeCell ref="A26:A30"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="E13:E16"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="E21:E41"/>
-    <mergeCell ref="A24:C25"/>
     <mergeCell ref="I14:I16"/>
     <mergeCell ref="I18:I22"/>
     <mergeCell ref="M2:M3"/>
@@ -9088,28 +9110,17 @@
     <mergeCell ref="M11:M12"/>
     <mergeCell ref="M14:M17"/>
     <mergeCell ref="M19:M21"/>
-    <mergeCell ref="M23:M26"/>
-    <mergeCell ref="M28:M55"/>
-    <mergeCell ref="Q2:Q5"/>
-    <mergeCell ref="Q7:Q13"/>
-    <mergeCell ref="Q15:Q18"/>
-    <mergeCell ref="Q20:Q22"/>
-    <mergeCell ref="Q24:Q25"/>
-    <mergeCell ref="U17:U25"/>
-    <mergeCell ref="U27:U28"/>
-    <mergeCell ref="U30:U39"/>
-    <mergeCell ref="U41:U47"/>
-    <mergeCell ref="W18:W19"/>
-    <mergeCell ref="Y18:Y20"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="Y25:Y26"/>
-    <mergeCell ref="Y28:Y30"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="Y35:Y38"/>
-    <mergeCell ref="Y40:Y41"/>
-    <mergeCell ref="Y43:Y45"/>
-    <mergeCell ref="Y47:Y49"/>
-    <mergeCell ref="Y51:Y60"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="S8:S10"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="Y1:AA1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="U2:U8"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9298,10 +9309,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="63" t="s">
         <v>570</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="64" t="s">
         <v>571</v>
       </c>
       <c r="C1" s="4" t="s">
@@ -9310,7 +9321,7 @@
       <c r="D1" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="F1" s="62" t="s">
+      <c r="F1" s="63" t="s">
         <v>574</v>
       </c>
       <c r="G1" s="61" t="s">
@@ -9322,7 +9333,7 @@
       <c r="I1" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="K1" s="62" t="s">
+      <c r="K1" s="63" t="s">
         <v>576</v>
       </c>
       <c r="L1" s="61" t="s">
@@ -9342,15 +9353,15 @@
       </c>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
       <c r="C2" s="4" t="s">
         <v>578</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="F2" s="62"/>
+      <c r="F2" s="63"/>
       <c r="G2" s="61"/>
       <c r="H2" s="4" t="s">
         <v>578</v>
@@ -9358,7 +9369,7 @@
       <c r="I2" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="K2" s="62"/>
+      <c r="K2" s="63"/>
       <c r="L2" s="61"/>
       <c r="M2" s="4" t="s">
         <v>578</v>
@@ -9372,15 +9383,15 @@
       </c>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="64"/>
       <c r="C3" s="4" t="s">
         <v>581</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="F3" s="62"/>
+      <c r="F3" s="63"/>
       <c r="G3" s="61"/>
       <c r="H3" s="4" t="s">
         <v>581</v>
@@ -9388,7 +9399,7 @@
       <c r="I3" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="K3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="L3" s="61"/>
       <c r="M3" s="4" t="s">
         <v>581</v>
@@ -9402,15 +9413,15 @@
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
       <c r="C4" s="4" t="s">
         <v>584</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="F4" s="62"/>
+      <c r="F4" s="63"/>
       <c r="G4" s="61"/>
       <c r="H4" s="4" t="s">
         <v>584</v>
@@ -9418,7 +9429,7 @@
       <c r="I4" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="K4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="L4" s="61"/>
       <c r="M4" s="4" t="s">
         <v>584</v>
@@ -9432,15 +9443,15 @@
       </c>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="62"/>
-      <c r="B5" s="63"/>
+      <c r="A5" s="63"/>
+      <c r="B5" s="64"/>
       <c r="C5" s="4" t="s">
         <v>588</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="F5" s="62"/>
+      <c r="F5" s="63"/>
       <c r="G5" s="61"/>
       <c r="H5" s="4" t="s">
         <v>588</v>
@@ -9448,7 +9459,7 @@
       <c r="I5" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="K5" s="62"/>
+      <c r="K5" s="63"/>
       <c r="L5" s="61"/>
       <c r="M5" s="4" t="s">
         <v>588</v>
@@ -9459,15 +9470,15 @@
       <c r="P5" s="61"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="62"/>
-      <c r="B6" s="63"/>
+      <c r="A6" s="63"/>
+      <c r="B6" s="64"/>
       <c r="C6" s="4" t="s">
         <v>592</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="F6" s="62"/>
+      <c r="F6" s="63"/>
       <c r="G6" s="61"/>
       <c r="H6" s="4" t="s">
         <v>592</v>
@@ -9475,7 +9486,7 @@
       <c r="I6" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="K6" s="62"/>
+      <c r="K6" s="63"/>
       <c r="L6" s="61"/>
       <c r="M6" s="4" t="s">
         <v>592</v>
@@ -9486,15 +9497,15 @@
       <c r="P6" s="61"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="62"/>
-      <c r="B7" s="63"/>
+      <c r="A7" s="63"/>
+      <c r="B7" s="64"/>
       <c r="C7" s="4" t="s">
         <v>595</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="F7" s="62"/>
+      <c r="F7" s="63"/>
       <c r="G7" s="61"/>
       <c r="H7" s="4" t="s">
         <v>595</v>
@@ -9505,8 +9516,8 @@
       <c r="P7" s="61"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="62"/>
-      <c r="B8" s="63"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="64"/>
       <c r="C8" s="4" t="s">
         <v>597</v>
       </c>
@@ -9522,15 +9533,15 @@
       <c r="P8" s="61"/>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="62"/>
-      <c r="B9" s="63"/>
+      <c r="A9" s="63"/>
+      <c r="B9" s="64"/>
       <c r="C9" s="4" t="s">
         <v>600</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="F9" s="62" t="s">
+      <c r="F9" s="63" t="s">
         <v>602</v>
       </c>
       <c r="G9" s="61" t="s">
@@ -9545,15 +9556,15 @@
       <c r="K9"/>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="62"/>
-      <c r="B10" s="63"/>
+      <c r="A10" s="63"/>
+      <c r="B10" s="64"/>
       <c r="C10" s="4" t="s">
         <v>604</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="F10" s="62"/>
+      <c r="F10" s="63"/>
       <c r="G10" s="61"/>
       <c r="H10" s="4" t="s">
         <v>578</v>
@@ -9569,7 +9580,7 @@
       </c>
     </row>
     <row r="11" spans="1:17">
-      <c r="F11" s="62"/>
+      <c r="F11" s="63"/>
       <c r="G11" s="61"/>
       <c r="H11" s="4" t="s">
         <v>581</v>
@@ -9580,10 +9591,10 @@
       <c r="K11"/>
     </row>
     <row r="12" spans="1:17" ht="49.5">
-      <c r="A12" s="62" t="s">
+      <c r="A12" s="63" t="s">
         <v>609</v>
       </c>
-      <c r="B12" s="63" t="s">
+      <c r="B12" s="64" t="s">
         <v>610</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -9592,7 +9603,7 @@
       <c r="D12" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="F12" s="62"/>
+      <c r="F12" s="63"/>
       <c r="G12" s="61"/>
       <c r="H12" s="4" t="s">
         <v>584</v>
@@ -9608,15 +9619,15 @@
       </c>
     </row>
     <row r="13" spans="1:17">
-      <c r="A13" s="62"/>
-      <c r="B13" s="63"/>
+      <c r="A13" s="63"/>
+      <c r="B13" s="64"/>
       <c r="C13" s="4" t="s">
         <v>578</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="F13" s="62"/>
+      <c r="F13" s="63"/>
       <c r="G13" s="61"/>
       <c r="H13" s="4" t="s">
         <v>588</v>
@@ -9628,15 +9639,15 @@
       <c r="L13" s="21"/>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="62"/>
-      <c r="B14" s="63"/>
+      <c r="A14" s="63"/>
+      <c r="B14" s="64"/>
       <c r="C14" s="4" t="s">
         <v>581</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="F14" s="62"/>
+      <c r="F14" s="63"/>
       <c r="G14" s="61"/>
       <c r="H14" s="4" t="s">
         <v>592</v>
@@ -9644,7 +9655,7 @@
       <c r="I14" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="K14" s="62" t="s">
+      <c r="K14" s="63" t="s">
         <v>613</v>
       </c>
       <c r="L14" s="61" t="s">
@@ -9658,15 +9669,15 @@
       </c>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="62"/>
-      <c r="B15" s="63"/>
+      <c r="A15" s="63"/>
+      <c r="B15" s="64"/>
       <c r="C15" s="4" t="s">
         <v>584</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="K15" s="62"/>
+      <c r="K15" s="63"/>
       <c r="L15" s="61"/>
       <c r="M15" s="4" t="s">
         <v>617</v>
@@ -9676,15 +9687,15 @@
       </c>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="62"/>
-      <c r="B16" s="63"/>
+      <c r="A16" s="63"/>
+      <c r="B16" s="64"/>
       <c r="C16" s="4" t="s">
         <v>588</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="F16" s="62" t="s">
+      <c r="F16" s="63" t="s">
         <v>620</v>
       </c>
       <c r="G16" s="61"/>
@@ -9696,15 +9707,15 @@
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="62"/>
-      <c r="B17" s="63"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="64"/>
       <c r="C17" s="4" t="s">
         <v>592</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="F17" s="62"/>
+      <c r="F17" s="63"/>
       <c r="G17" s="61"/>
       <c r="H17" s="4" t="s">
         <v>578</v>
@@ -9720,7 +9731,7 @@
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="F18" s="62"/>
+      <c r="F18" s="63"/>
       <c r="G18" s="61"/>
       <c r="H18" s="4" t="s">
         <v>581</v>
@@ -9730,7 +9741,7 @@
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="F19" s="62"/>
+      <c r="F19" s="63"/>
       <c r="G19" s="61"/>
       <c r="H19" s="4" t="s">
         <v>584</v>
@@ -9751,24 +9762,24 @@
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="72" t="s">
+      <c r="A22" s="62" t="s">
         <v>933</v>
       </c>
-      <c r="B22" s="72"/>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="72"/>
-      <c r="O22" s="72"/>
-      <c r="P22" s="72"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="62"/>
+      <c r="P22" s="62"/>
     </row>
     <row r="23" spans="1:16">
       <c r="K23" s="4" t="s">
@@ -9846,13 +9857,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="65" t="s">
         <v>637</v>
       </c>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
     </row>
     <row r="2" spans="1:10">
       <c r="B2" s="4" t="s">
@@ -9883,7 +9894,7 @@
       <c r="D3" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="E3" s="63" t="s">
+      <c r="E3" s="64" t="s">
         <v>645</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -9900,7 +9911,7 @@
       <c r="D4" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="E4" s="63"/>
+      <c r="E4" s="64"/>
       <c r="F4" s="4" t="s">
         <v>648</v>
       </c>
@@ -9915,7 +9926,7 @@
       <c r="D5" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="E5" s="63"/>
+      <c r="E5" s="64"/>
       <c r="F5" s="4" t="s">
         <v>650</v>
       </c>
@@ -9954,7 +9965,7 @@
       <c r="D7" s="61" t="s">
         <v>659</v>
       </c>
-      <c r="E7" s="63" t="s">
+      <c r="E7" s="64" t="s">
         <v>660</v>
       </c>
       <c r="F7" s="4" t="s">
@@ -9969,14 +9980,14 @@
       <c r="B8" s="61"/>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
-      <c r="E8" s="63"/>
+      <c r="E8" s="64"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="61"/>
       <c r="B9" s="61"/>
       <c r="C9" s="61"/>
       <c r="D9" s="61"/>
-      <c r="E9" s="63"/>
+      <c r="E9" s="64"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="23" t="s">
@@ -10189,6 +10200,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E11:E13"/>
     <mergeCell ref="F1:J1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="A3:A5"/>
@@ -10197,11 +10213,6 @@
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10387,11 +10398,11 @@
       <c r="B1" s="15" t="s">
         <v>741</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="66" t="s">
         <v>742</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
     </row>
     <row r="2" spans="1:7">
       <c r="E2" s="16" t="s">
